--- a/categorie.xlsx
+++ b/categorie.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/61197a8ee6b2bca5/Python/dev/5x1000.local/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/61197a8ee6b2bca5/Documenti/Siti Internert/5x1000_prod/5x1000.almagioni.com/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="11_38BE3B91B9C9449F3341FF0824850D43D1462CD6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94F30AA0-8193-4F2B-9137-F2306B714F96}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{F52654AE-7C45-4903-9879-BE0AF04BF6B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDEE353E-DEB2-46C4-8AD7-793C9E86C90C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="65">
   <si>
     <t>Categora</t>
   </si>
@@ -191,13 +191,53 @@
   </si>
   <si>
     <t>https://www.agenziaentrate.gov.it/portale/ricerca-scientifica-ammessi-ed-esclusi-5x1000-2020</t>
+  </si>
+  <si>
+    <t>https://www.agenziaentrate.gov.it/portale/enti-del-terzo-settore</t>
+  </si>
+  <si>
+    <t>Enti del Terzo Settore</t>
+  </si>
+  <si>
+    <t>https://www.agenziaentrate.gov.it/portale/ricerca-scientifica2</t>
+  </si>
+  <si>
+    <r>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color theme="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ricerca scientifica</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.agenziaentrate.gov.it/portale/associazioni-sportive-dilettantistiche1</t>
+  </si>
+  <si>
+    <t>https://www.agenziaentrate.gov.it/portale/enti-dei-beni-culturali-e-paesaggistici</t>
+  </si>
+  <si>
+    <t>https://www.agenziaentrate.gov.it/portale/enti-gestori-delle-aree-protette</t>
+  </si>
+  <si>
+    <t>https://www.agenziaentrate.gov.it/portale/ricerca-sanitaria1</t>
+  </si>
+  <si>
+    <t>https://www.agenziaentrate.gov.it/portale/attivit%C3%A0-svolte-dai-comuni</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -222,6 +262,14 @@
       <color rgb="FF1A1A1A"/>
       <name val="Font Awesome 5 Free"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -237,7 +285,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -260,12 +308,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -275,6 +334,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -491,10 +554,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="48.5703125" bestFit="1" customWidth="1"/>
@@ -590,7 +653,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" thickBot="1">
+    <row r="9" spans="1:3" thickBot="1">
       <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
@@ -601,7 +664,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="10" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="6" t="s">
         <v>18</v>
       </c>
@@ -612,7 +675,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="11" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
@@ -623,7 +686,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="12" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="6" t="s">
         <v>20</v>
       </c>
@@ -634,7 +697,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1" thickBot="1">
+    <row r="13" spans="1:3" thickBot="1">
       <c r="A13" s="6" t="s">
         <v>21</v>
       </c>
@@ -645,7 +708,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="14" spans="1:3" hidden="1" thickBot="1">
+    <row r="14" spans="1:3" thickBot="1">
       <c r="A14" s="6" t="s">
         <v>22</v>
       </c>
@@ -656,7 +719,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="15" spans="1:3" hidden="1" thickBot="1">
+    <row r="15" spans="1:3" thickBot="1">
       <c r="A15" s="6" t="s">
         <v>23</v>
       </c>
@@ -667,7 +730,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="16" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
@@ -678,7 +741,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="17" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="6" t="s">
         <v>18</v>
       </c>
@@ -689,7 +752,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="18" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="6" t="s">
         <v>19</v>
       </c>
@@ -700,7 +763,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="19" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="6" t="s">
         <v>20</v>
       </c>
@@ -711,7 +774,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="20" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="6" t="s">
         <v>28</v>
       </c>
@@ -722,7 +785,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="21" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="6" t="s">
         <v>30</v>
       </c>
@@ -733,7 +796,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="22" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="6" t="s">
         <v>32</v>
       </c>
@@ -744,7 +807,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="23" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="6" t="s">
         <v>34</v>
       </c>
@@ -755,7 +818,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="24" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="6" t="s">
         <v>18</v>
       </c>
@@ -766,7 +829,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="25" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="6" t="s">
         <v>19</v>
       </c>
@@ -777,7 +840,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="26" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="6" t="s">
         <v>20</v>
       </c>
@@ -788,7 +851,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="27" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A27" s="6" t="s">
         <v>21</v>
       </c>
@@ -799,7 +862,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="28" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A28" s="6" t="s">
         <v>22</v>
       </c>
@@ -810,7 +873,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="29" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A29" s="6" t="s">
         <v>23</v>
       </c>
@@ -821,7 +884,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="30" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A30" s="3" t="s">
         <v>34</v>
       </c>
@@ -832,7 +895,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="31" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A31" s="6" t="s">
         <v>18</v>
       </c>
@@ -843,7 +906,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="32" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A32" s="6" t="s">
         <v>19</v>
       </c>
@@ -854,7 +917,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="33" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A33" s="6" t="s">
         <v>20</v>
       </c>
@@ -865,7 +928,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="34" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A34" s="6" t="s">
         <v>21</v>
       </c>
@@ -876,7 +939,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="35" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A35" s="6" t="s">
         <v>22</v>
       </c>
@@ -887,7 +950,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="36" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A36" s="6" t="s">
         <v>23</v>
       </c>
@@ -898,7 +961,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="37" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A37" s="6" t="s">
         <v>34</v>
       </c>
@@ -909,7 +972,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="38" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A38" s="6" t="s">
         <v>18</v>
       </c>
@@ -920,7 +983,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="39" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A39" s="6" t="s">
         <v>19</v>
       </c>
@@ -931,7 +994,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="40" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A40" s="6" t="s">
         <v>20</v>
       </c>
@@ -942,7 +1005,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="41" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A41" s="6" t="s">
         <v>21</v>
       </c>
@@ -953,7 +1016,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="42" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A42" s="6" t="s">
         <v>22</v>
       </c>
@@ -964,7 +1027,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="43" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A43" s="6" t="s">
         <v>23</v>
       </c>
@@ -975,14 +1038,85 @@
         <v>2019</v>
       </c>
     </row>
+    <row r="44" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A44" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" s="7">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A45" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45" s="7">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A46" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C46" s="7">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A47" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C47" s="7">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A48" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C48" s="7">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A49" t="s">
+        <v>22</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C49" s="7">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A50" t="s">
+        <v>23</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C50" s="7">
+        <v>2025</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C43" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="2024"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:C43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://www.agenziaentrate.gov.it/portale/enti-del-terzo-settore-e-onlus-2024" xr:uid="{0746E94C-A9B6-4BDA-9560-426C170FE9FD}"/>
     <hyperlink ref="B2" r:id="rId2" xr:uid="{30D31D35-DAEB-41FE-8584-24E31F75519E}"/>
@@ -1068,6 +1202,16 @@
     <hyperlink ref="B42" r:id="rId82" xr:uid="{BF09495E-2AD3-4A0E-ADE1-BAEE07B3C691}"/>
     <hyperlink ref="A43" r:id="rId83" display="https://www.agenziaentrate.gov.it/portale/enti-gestori-delle-aree-protette-2019" xr:uid="{E85BC395-BE9A-4A48-9D6D-518BA12858E5}"/>
     <hyperlink ref="B43" r:id="rId84" xr:uid="{6D46722B-E5A6-4B53-B2CE-6CDEBEABFE55}"/>
+    <hyperlink ref="A44" r:id="rId85" display="https://www.agenziaentrate.gov.it/portale/enti-del-terzo-settore" xr:uid="{26C3A281-4312-42D3-84D4-BF52A124E875}"/>
+    <hyperlink ref="A45" r:id="rId86" display="https://www.agenziaentrate.gov.it/portale/ricerca-scientifica2" xr:uid="{EF3700A6-7996-4AC9-BF9D-D8EAA500938B}"/>
+    <hyperlink ref="A46" r:id="rId87" display="https://www.agenziaentrate.gov.it/portale/ricerca-sanitaria1" xr:uid="{C4329830-234D-4885-8CCE-F9672A307F21}"/>
+    <hyperlink ref="A47" r:id="rId88" display="https://www.agenziaentrate.gov.it/portale/attivit%C3%A0-svolte-dai-comuni" xr:uid="{A28725AD-CED4-4C2F-9015-9A038538E47E}"/>
+    <hyperlink ref="B44" r:id="rId89" xr:uid="{DCF1861D-8490-420C-8720-0E9B468E5F6C}"/>
+    <hyperlink ref="B45" r:id="rId90" xr:uid="{265A47EB-B25B-4293-88CE-7EF7BFA25591}"/>
+    <hyperlink ref="B47" r:id="rId91" xr:uid="{B3C913D7-7234-44DB-8783-E33DE576974E}"/>
+    <hyperlink ref="B48" r:id="rId92" xr:uid="{F891760F-302F-46EF-B174-64DA66CA1D24}"/>
+    <hyperlink ref="B49" r:id="rId93" xr:uid="{101FC377-40F0-4B32-8557-B8986DD09DCC}"/>
+    <hyperlink ref="B50" r:id="rId94" xr:uid="{4497CAC4-1492-491E-9892-1BD4ED779D36}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/categorie.xlsx
+++ b/categorie.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/61197a8ee6b2bca5/Documenti/Siti Internert/5x1000_prod/5x1000.almagioni.com/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{F52654AE-7C45-4903-9879-BE0AF04BF6B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDEE353E-DEB2-46C4-8AD7-793C9E86C90C}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="11_38BE3B91B9C9449F3341FF0824850D43D1462CD6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8AF3F87-6569-4806-9C4A-326705CB901A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
+    <sheet name="Foglio2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$C$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$C$50</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="64">
   <si>
     <t>Categora</t>
   </si>
@@ -193,51 +194,35 @@
     <t>https://www.agenziaentrate.gov.it/portale/ricerca-scientifica-ammessi-ed-esclusi-5x1000-2020</t>
   </si>
   <si>
-    <t>https://www.agenziaentrate.gov.it/portale/enti-del-terzo-settore</t>
-  </si>
-  <si>
     <t>Enti del Terzo Settore</t>
   </si>
   <si>
+    <t>https://www.agenziaentrate.gov.it/portale/elenchi-ammessi-ed-esclusi2#:~:text=in%20formato%20pdf-,Enti%20del%20Terzo%20Settore,-Ricerca%20scientifica</t>
+  </si>
+  <si>
     <t>https://www.agenziaentrate.gov.it/portale/ricerca-scientifica2</t>
   </si>
   <si>
-    <r>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color theme="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Ricerca scientifica</t>
-    </r>
-  </si>
-  <si>
-    <t>https://www.agenziaentrate.gov.it/portale/associazioni-sportive-dilettantistiche1</t>
-  </si>
-  <si>
-    <t>https://www.agenziaentrate.gov.it/portale/enti-dei-beni-culturali-e-paesaggistici</t>
-  </si>
-  <si>
-    <t>https://www.agenziaentrate.gov.it/portale/enti-gestori-delle-aree-protette</t>
-  </si>
-  <si>
-    <t>https://www.agenziaentrate.gov.it/portale/ricerca-sanitaria1</t>
-  </si>
-  <si>
-    <t>https://www.agenziaentrate.gov.it/portale/attivit%C3%A0-svolte-dai-comuni</t>
+    <t>https://www.agenziaentrate.gov.it/portale/elenchi-ammessi-ed-esclusi2#:~:text=Ricerca%20scientifica-,Ricerca%20sanitaria,-Attivit%C3%A0%20svolte%20dai</t>
+  </si>
+  <si>
+    <t>https://www.agenziaentrate.gov.it/portale/elenchi-ammessi-ed-esclusi2#:~:text=Attivit%C3%A0%20svolte%20dai%20comuni</t>
+  </si>
+  <si>
+    <t>https://www.agenziaentrate.gov.it/portale/elenchi-ammessi-ed-esclusi2#:~:text=svolte%20dai%20comuni-,Associazioni%20sportive%20dilettantistiche,-Enti%20dei%20beni</t>
+  </si>
+  <si>
+    <t>https://www.agenziaentrate.gov.it/portale/elenchi-ammessi-ed-esclusi2#:~:text=Associazioni%20sportive%20dilettantistiche-,Enti%20dei%20beni%20culturali%20e%20paesaggistici,-Enti%20gestori%20delle</t>
+  </si>
+  <si>
+    <t>https://www.agenziaentrate.gov.it/portale/elenchi-ammessi-ed-esclusi2#:~:text=culturali%20e%20paesaggistici-,Enti%20gestori%20delle%20aree%20protette,-L%27Agenzia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -262,14 +247,6 @@
       <color rgb="FF1A1A1A"/>
       <name val="Font Awesome 5 Free"/>
     </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -285,7 +262,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -308,17 +285,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -334,10 +300,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -577,91 +541,91 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="13.5" thickBot="1">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B9" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C9" s="5">
         <v>2024</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="5">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="5">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" thickBot="1">
-      <c r="A5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="5">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" thickBot="1">
-      <c r="A6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="5">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" thickBot="1">
-      <c r="A7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="5">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" thickBot="1">
-      <c r="A8" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" thickBot="1">
-      <c r="A9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="5">
-        <v>2023</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
@@ -669,10 +633,10 @@
         <v>18</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C10" s="5">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
@@ -680,21 +644,21 @@
         <v>19</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C11" s="5">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" thickBot="1">
       <c r="A12" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C12" s="5">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="13" spans="1:3" thickBot="1">
@@ -702,10 +666,10 @@
         <v>21</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C13" s="5">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="14" spans="1:3" thickBot="1">
@@ -713,10 +677,10 @@
         <v>22</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="15" spans="1:3" thickBot="1">
@@ -724,21 +688,21 @@
         <v>23</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C15" s="5">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" thickBot="1">
+      <c r="A16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
         <v>2023</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A16" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="5">
-        <v>2022</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
@@ -746,10 +710,10 @@
         <v>18</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C17" s="5">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
@@ -757,10 +721,10 @@
         <v>19</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C18" s="5">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
@@ -768,54 +732,54 @@
         <v>20</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C19" s="5">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" thickBot="1">
+      <c r="A20" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="5">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" thickBot="1">
+      <c r="A21" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="5">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" thickBot="1">
+      <c r="A22" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="5">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="5">
         <v>2022</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A20" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="5">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A21" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="5">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A22" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="5">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A23" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="5">
-        <v>2021</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
@@ -823,10 +787,10 @@
         <v>18</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C24" s="5">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
@@ -834,10 +798,10 @@
         <v>19</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C25" s="5">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
@@ -845,54 +809,54 @@
         <v>20</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C26" s="5">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A27" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C27" s="5">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A28" s="6" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A29" s="6" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C29" s="5">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A30" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="5">
         <v>2021</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A30" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C30" s="5">
-        <v>2020</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
@@ -900,10 +864,10 @@
         <v>18</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="C31" s="5">
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
@@ -911,10 +875,10 @@
         <v>19</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C32" s="5">
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
@@ -922,10 +886,10 @@
         <v>20</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C33" s="5">
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
@@ -933,10 +897,10 @@
         <v>21</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C34" s="5">
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
@@ -944,10 +908,10 @@
         <v>22</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C35" s="5">
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
@@ -955,21 +919,21 @@
         <v>23</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C36" s="5">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A37" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="5">
         <v>2020</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A37" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C37" s="5">
-        <v>2019</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
@@ -977,10 +941,10 @@
         <v>18</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C38" s="5">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
@@ -988,10 +952,10 @@
         <v>19</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C39" s="5">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
@@ -999,10 +963,10 @@
         <v>20</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C40" s="5">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
@@ -1010,10 +974,10 @@
         <v>21</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C41" s="5">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
@@ -1021,10 +985,10 @@
         <v>22</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C42" s="5">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
@@ -1032,187 +996,201 @@
         <v>23</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C43" s="5">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A44" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C44" s="5">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C45" s="5">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A46" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C46" s="5">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A47" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47" s="5">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A48" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C48" s="5">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A49" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" s="5">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A50" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C43" s="5">
+      <c r="C50" s="5">
         <v>2019</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A44" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C44" s="7">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A45" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C45" s="7">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A46" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C46" s="7">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A47" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C47" s="7">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A48" t="s">
-        <v>21</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C48" s="7">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A49" t="s">
-        <v>22</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C49" s="7">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A50" t="s">
-        <v>23</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C50" s="7">
-        <v>2025</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:C50" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="https://www.agenziaentrate.gov.it/portale/enti-del-terzo-settore-e-onlus-2024" xr:uid="{0746E94C-A9B6-4BDA-9560-426C170FE9FD}"/>
-    <hyperlink ref="B2" r:id="rId2" xr:uid="{30D31D35-DAEB-41FE-8584-24E31F75519E}"/>
-    <hyperlink ref="A3" r:id="rId3" display="https://www.agenziaentrate.gov.it/portale/ricerca-scientifica-2024" xr:uid="{F1F7AF15-DA2C-4E02-BC15-B87572759553}"/>
-    <hyperlink ref="B3" r:id="rId4" xr:uid="{5198BC62-CBD5-4CD4-B28B-23E4DE3A47FF}"/>
-    <hyperlink ref="A4" r:id="rId5" display="https://www.agenziaentrate.gov.it/portale/ricerca-sanitaria-2024" xr:uid="{B2B0FDC3-8D60-426C-B6A2-EE7E293064CC}"/>
-    <hyperlink ref="B4" r:id="rId6" xr:uid="{91DE0745-0C6C-4B23-810E-23F93787A5F2}"/>
-    <hyperlink ref="A5" r:id="rId7" display="https://www.agenziaentrate.gov.it/portale/attivit%C3%A0-svolte-dai-comuni-2024" xr:uid="{A8ED647E-0122-4E28-9F3B-D5C740C35384}"/>
-    <hyperlink ref="B5" r:id="rId8" xr:uid="{CBA5CC3E-3121-4A86-919C-EB8E0529C071}"/>
-    <hyperlink ref="A6" r:id="rId9" display="https://www.agenziaentrate.gov.it/portale/associazioni-sportive-dilettantistiche-2024" xr:uid="{7901A471-EF6F-4134-9979-1C8AB5CD7DB8}"/>
-    <hyperlink ref="B6" r:id="rId10" xr:uid="{E3BB5D46-D4E9-4D40-A770-53C77705B309}"/>
-    <hyperlink ref="A7" r:id="rId11" display="https://www.agenziaentrate.gov.it/portale/enti-dei-beni-culturali-e-paesaggistici-2024" xr:uid="{67F61C3C-BA70-449F-AA2F-0594A7373756}"/>
-    <hyperlink ref="B7" r:id="rId12" xr:uid="{187B4948-CF43-4452-922B-DD40F6C17C4E}"/>
-    <hyperlink ref="A8" r:id="rId13" display="https://www.agenziaentrate.gov.it/portale/enti-gestori-delle-aree-protette-2024" xr:uid="{04293583-0231-42B0-9B6D-67248923F9C5}"/>
-    <hyperlink ref="B8" r:id="rId14" xr:uid="{167AA414-07C8-41DF-BF22-3DAC32864916}"/>
-    <hyperlink ref="A9" r:id="rId15" display="https://www.agenziaentrate.gov.it/portale/enti-del-terzo-settore-e-onlus-2023" xr:uid="{085E4620-B75D-484A-99D5-04916EDF073A}"/>
-    <hyperlink ref="B9" r:id="rId16" xr:uid="{A57C72D1-090D-406B-B8EA-86833706DB2E}"/>
-    <hyperlink ref="A10" r:id="rId17" display="https://www.agenziaentrate.gov.it/portale/ricerca-scientifica-2023" xr:uid="{0BF1B728-0DCE-4F1D-AFC7-184DC487015B}"/>
-    <hyperlink ref="B10" r:id="rId18" xr:uid="{2313E86F-EBDA-44D0-A425-FA79E0F21639}"/>
-    <hyperlink ref="A11" r:id="rId19" display="https://www.agenziaentrate.gov.it/portale/ricerca-sanitaria-2023" xr:uid="{FCEFB34E-674A-43E6-8F67-D359B003339A}"/>
-    <hyperlink ref="B11" r:id="rId20" xr:uid="{5DEE8BA2-05B4-46E5-B403-548902D74E52}"/>
-    <hyperlink ref="A12" r:id="rId21" display="https://www.agenziaentrate.gov.it/portale/attivita-svolte-dai-comuni-2023" xr:uid="{8AC218D4-94E2-4F1A-A383-31576D3DEB3F}"/>
-    <hyperlink ref="B12" r:id="rId22" xr:uid="{1930118C-E720-4212-82EF-49AE2802BE33}"/>
-    <hyperlink ref="A13" r:id="rId23" display="https://www.agenziaentrate.gov.it/portale/associazioni-sportive-dilettantistiche-2023" xr:uid="{15B89EFB-1F1F-4A61-A563-3A8337E23B04}"/>
-    <hyperlink ref="B13" r:id="rId24" xr:uid="{7E186F42-B301-4580-86D3-ADEAE1B10C86}"/>
-    <hyperlink ref="A14" r:id="rId25" display="https://www.agenziaentrate.gov.it/portale/enti-dei-beni-culturali-e-paesaggistici-2023" xr:uid="{A7A4309E-F81D-4C64-AA74-E7E3EBD52B0B}"/>
-    <hyperlink ref="B14" r:id="rId26" xr:uid="{C6E01281-1AE6-4901-8DAF-DF706FAA7B87}"/>
-    <hyperlink ref="A15" r:id="rId27" display="https://www.agenziaentrate.gov.it/portale/Enti-gestori-delle-aree-protette-2023" xr:uid="{25407C4D-FCCC-4241-BFDD-2ED1508E679F}"/>
-    <hyperlink ref="B15" r:id="rId28" xr:uid="{D2A3AD40-F054-4CB9-B23D-E0E7CB1FF5F5}"/>
-    <hyperlink ref="A16" r:id="rId29" display="https://www.agenziaentrate.gov.it/portale/enti-del-terzo-settore-e-onlus-23" xr:uid="{9AEE31A2-AF07-48B6-BD31-43782B2AE493}"/>
-    <hyperlink ref="B16" r:id="rId30" xr:uid="{DC38C048-5DEA-4205-8682-8747199D0A66}"/>
-    <hyperlink ref="A17" r:id="rId31" display="https://www.agenziaentrate.gov.it/portale/ricerca-scientifica-23" xr:uid="{4D97CD3A-691C-4E94-9119-A8CE36AEF0F9}"/>
-    <hyperlink ref="B17" r:id="rId32" xr:uid="{44F182CE-2362-40AB-9947-B665627BA327}"/>
-    <hyperlink ref="A18" r:id="rId33" display="https://www.agenziaentrate.gov.it/portale/ricerca-sanitaria" xr:uid="{6B2ACB9C-5F1E-4B8D-AAD9-40779502F7C0}"/>
-    <hyperlink ref="B18" r:id="rId34" xr:uid="{6167BE59-0896-4BF1-95A7-ABC7932C8832}"/>
-    <hyperlink ref="A19" r:id="rId35" display="https://www.agenziaentrate.gov.it/portale/attivita-svolte-dai-comuni-23" xr:uid="{A5FFFACC-7FC2-4095-A036-E4F0996D6773}"/>
-    <hyperlink ref="B19" r:id="rId36" xr:uid="{9AFAC604-E64A-4F31-871C-7B382794034C}"/>
-    <hyperlink ref="A20" r:id="rId37" display="https://www.agenziaentrate.gov.it/portale/associazioni-sportive-dilettantistiche-asd-23" xr:uid="{494E0552-E012-419B-B906-B0A213732E2B}"/>
-    <hyperlink ref="B20" r:id="rId38" xr:uid="{8A572FAA-1F83-4626-9267-199301E2975B}"/>
-    <hyperlink ref="A21" r:id="rId39" display="https://www.agenziaentrate.gov.it/portale/beni-culturali-e-paesaggistici-23" xr:uid="{6A643E59-4432-4D8D-A950-ED24B3B8E28D}"/>
-    <hyperlink ref="B21" r:id="rId40" xr:uid="{6DA59AD1-E4A2-4816-9728-657C4FC30FCE}"/>
-    <hyperlink ref="A22" r:id="rId41" display="https://www.agenziaentrate.gov.it/portale/documents/20143/4443043/5XM-AF2022+-+AREE+PROTETTE+-+AMMESSI.pdf/51ed59be-2418-4db3-39c5-61ab02064f31?t=1687459725347" xr:uid="{CC4EEEDC-80FE-43B8-B4CF-9D66911363A1}"/>
-    <hyperlink ref="B22" r:id="rId42" xr:uid="{2566C3DA-FFFE-4252-94BF-8881E575DFFC}"/>
-    <hyperlink ref="A23" r:id="rId43" display="https://www.agenziaentrate.gov.it/portale/enti-volontariato-ammessi-esclusi-af-2021" xr:uid="{9BA21E0C-3739-40DF-928D-9E486BE298D7}"/>
-    <hyperlink ref="B23" r:id="rId44" xr:uid="{1D149A7A-71C3-45F4-8183-05B3772DF65C}"/>
-    <hyperlink ref="A24" r:id="rId45" display="https://www.agenziaentrate.gov.it/portale/ricerca-scientifica-ammessi-esclusi-af-2021" xr:uid="{16CA7436-978D-436A-A145-2219F6A5B89D}"/>
-    <hyperlink ref="B24" r:id="rId46" xr:uid="{F1C12662-2C07-4026-B6E3-BDC34A17ED64}"/>
-    <hyperlink ref="A25" r:id="rId47" display="https://www.agenziaentrate.gov.it/portale/ricerca-sanitaria-ammessi-esclusi-af-2021" xr:uid="{E9C79AAF-AB8D-457A-94E6-1290C2AD8224}"/>
-    <hyperlink ref="B25" r:id="rId48" xr:uid="{A76D6B3E-9171-4A69-A861-1FE384E8780B}"/>
-    <hyperlink ref="A26" r:id="rId49" display="https://www.agenziaentrate.gov.it/portale/attivit%C3%A0-svolte-dai-comuni-ammessi-esclusi-af-2021" xr:uid="{E71B9303-433E-424D-9777-DED52F66AA86}"/>
-    <hyperlink ref="B26" r:id="rId50" xr:uid="{E462E970-138F-4E58-A964-4B006459EF58}"/>
-    <hyperlink ref="A27" r:id="rId51" display="https://www.agenziaentrate.gov.it/portale/asd-ammessi-esclusi-af-2021" xr:uid="{764031F2-DE1C-49D3-BC48-4A1E1B88CFC1}"/>
-    <hyperlink ref="B27" r:id="rId52" xr:uid="{539B33DD-6A26-48A1-9E08-C88C2DE0118B}"/>
-    <hyperlink ref="A28" r:id="rId53" display="https://www.agenziaentrate.gov.it/portale/enti-dei-beni-culturali-e-paesaggistici-af-2021" xr:uid="{6E07C45A-0CC9-451B-9A44-62CF48B5DDB2}"/>
-    <hyperlink ref="B28" r:id="rId54" xr:uid="{D15CB439-E862-438C-83AA-44446BB01F0D}"/>
-    <hyperlink ref="A29" r:id="rId55" display="https://www.agenziaentrate.gov.it/portale/enti-gestori-aree-protette-ammessi-esclusi-af-2021" xr:uid="{C148DC0D-AC6F-4A42-B621-B73C1F43EFC1}"/>
-    <hyperlink ref="B29" r:id="rId56" xr:uid="{F09EC905-FEED-44F2-9897-181EEF93E417}"/>
-    <hyperlink ref="A30" r:id="rId57" display="https://www.agenziaentrate.gov.it/portale/ammessi-ed-esclusi-enti-del-volontariato-5x1000-2020" xr:uid="{47EB5E9E-58EA-4AEB-ADF6-35FA9C29CCC1}"/>
-    <hyperlink ref="B30" r:id="rId58" xr:uid="{65EE7DC2-3FEE-4E1A-B0C9-EF80822986AD}"/>
-    <hyperlink ref="A31" r:id="rId59" display="https://www.agenziaentrate.gov.it/portale/ricerca-scientifica-ammessi-ed-esclusi-5x1000-2020" xr:uid="{2ABBBE77-E908-44AF-A47A-298685FDB9A1}"/>
-    <hyperlink ref="B31" r:id="rId60" xr:uid="{92578B0D-0F12-49D1-9027-D9E69DAC86BF}"/>
-    <hyperlink ref="A32" r:id="rId61" display="https://www.agenziaentrate.gov.it/portale/ricerca-sanitaria-ammessi-esclusi-5x1000-2020" xr:uid="{1DF48004-D32B-4E4C-9702-E9C312287385}"/>
-    <hyperlink ref="B32" r:id="rId62" xr:uid="{37F5CDDA-36F0-437F-B9CC-D62C6616BA05}"/>
-    <hyperlink ref="A33" r:id="rId63" display="https://www.agenziaentrate.gov.it/portale/attivita-svolte-dai-comuni-ammessi-esclusi-5x1000-2020" xr:uid="{D8DD0AE9-1899-4BA6-8B0A-0F2D093B76DB}"/>
-    <hyperlink ref="B33" r:id="rId64" xr:uid="{99E94FAF-1EAA-42E2-B796-64CA7766A469}"/>
-    <hyperlink ref="A34" r:id="rId65" display="https://www.agenziaentrate.gov.it/portale/associazioni-sportive-dilettantistiche-ammessi-esclusi-5x1000-2020" xr:uid="{9301FF8E-783C-4D1D-A563-9B8D9103AAD2}"/>
-    <hyperlink ref="B34" r:id="rId66" xr:uid="{48DCD4A3-6030-497A-B517-4D00A042DBDA}"/>
-    <hyperlink ref="A35" r:id="rId67" display="https://www.agenziaentrate.gov.it/portale/enti-dei-beni-culturali-e-paesaggistici-ammessi-esclusi-5x1000-2020" xr:uid="{4895397C-8ABA-40E7-BD63-606256D85F4E}"/>
-    <hyperlink ref="B35" r:id="rId68" xr:uid="{5F032F00-8FA5-4008-9D68-61676A3EB666}"/>
-    <hyperlink ref="A36" r:id="rId69" display="https://www.agenziaentrate.gov.it/portale/enti-gestori-delle-aree-protette-esclusi-ammessi-5x1000-2020" xr:uid="{629A3CF7-2344-43A6-A2A9-FA8AA437DB5B}"/>
-    <hyperlink ref="B36" r:id="rId70" xr:uid="{CF95AB0E-0728-4EF7-A640-409F1CD4AB71}"/>
-    <hyperlink ref="A37" r:id="rId71" display="https://www.agenziaentrate.gov.it/portale/enti-del-volontariato-2019" xr:uid="{BBC1505A-8B11-42FD-9B9F-41209ACBA0FD}"/>
-    <hyperlink ref="B37" r:id="rId72" xr:uid="{C22762C1-D955-4AC5-94F5-1638121AC290}"/>
-    <hyperlink ref="A38" r:id="rId73" display="https://www.agenziaentrate.gov.it/portale/ricerca-scientifica1" xr:uid="{2C4CD3DE-CA60-415A-A009-7FFB1FD5D20F}"/>
-    <hyperlink ref="B38" r:id="rId74" xr:uid="{2C4AD919-3338-4279-AB57-269DBE61C6DF}"/>
-    <hyperlink ref="A39" r:id="rId75" display="https://www.agenziaentrate.gov.it/portale/ricerca-sanitaria-2019" xr:uid="{A48DD348-E1DA-41F4-BF94-AFD03AB52587}"/>
-    <hyperlink ref="B39" r:id="rId76" xr:uid="{08761D35-6CEF-4E66-AECF-7BDA34E3A352}"/>
-    <hyperlink ref="A40" r:id="rId77" display="https://www.agenziaentrate.gov.it/portale/attivit%C3%A0-svolte-dai-comuni-2019" xr:uid="{7F8062F9-1F41-498B-A000-15E8D2F515DB}"/>
-    <hyperlink ref="B40" r:id="rId78" xr:uid="{7B2C9579-C1F2-4F40-8472-1FB31040D65E}"/>
-    <hyperlink ref="A41" r:id="rId79" display="https://www.agenziaentrate.gov.it/portale/associazioni-sportive-dilettantistiche-2019" xr:uid="{616F6478-5442-4D2A-9453-58F1DE0936D1}"/>
-    <hyperlink ref="B41" r:id="rId80" xr:uid="{D31D3A05-1DD1-432D-83D1-DC41E796E6D0}"/>
-    <hyperlink ref="A42" r:id="rId81" display="https://www.agenziaentrate.gov.it/portale/enti-dei-beni-culturali-e-paesaggistici-2019" xr:uid="{354CF7D3-3609-4D21-B12B-983CA359AB53}"/>
-    <hyperlink ref="B42" r:id="rId82" xr:uid="{BF09495E-2AD3-4A0E-ADE1-BAEE07B3C691}"/>
-    <hyperlink ref="A43" r:id="rId83" display="https://www.agenziaentrate.gov.it/portale/enti-gestori-delle-aree-protette-2019" xr:uid="{E85BC395-BE9A-4A48-9D6D-518BA12858E5}"/>
-    <hyperlink ref="B43" r:id="rId84" xr:uid="{6D46722B-E5A6-4B53-B2CE-6CDEBEABFE55}"/>
-    <hyperlink ref="A44" r:id="rId85" display="https://www.agenziaentrate.gov.it/portale/enti-del-terzo-settore" xr:uid="{26C3A281-4312-42D3-84D4-BF52A124E875}"/>
-    <hyperlink ref="A45" r:id="rId86" display="https://www.agenziaentrate.gov.it/portale/ricerca-scientifica2" xr:uid="{EF3700A6-7996-4AC9-BF9D-D8EAA500938B}"/>
-    <hyperlink ref="A46" r:id="rId87" display="https://www.agenziaentrate.gov.it/portale/ricerca-sanitaria1" xr:uid="{C4329830-234D-4885-8CCE-F9672A307F21}"/>
-    <hyperlink ref="A47" r:id="rId88" display="https://www.agenziaentrate.gov.it/portale/attivit%C3%A0-svolte-dai-comuni" xr:uid="{A28725AD-CED4-4C2F-9015-9A038538E47E}"/>
-    <hyperlink ref="B44" r:id="rId89" xr:uid="{DCF1861D-8490-420C-8720-0E9B468E5F6C}"/>
-    <hyperlink ref="B45" r:id="rId90" xr:uid="{265A47EB-B25B-4293-88CE-7EF7BFA25591}"/>
-    <hyperlink ref="B47" r:id="rId91" xr:uid="{B3C913D7-7234-44DB-8783-E33DE576974E}"/>
-    <hyperlink ref="B48" r:id="rId92" xr:uid="{F891760F-302F-46EF-B174-64DA66CA1D24}"/>
-    <hyperlink ref="B49" r:id="rId93" xr:uid="{101FC377-40F0-4B32-8557-B8986DD09DCC}"/>
-    <hyperlink ref="B50" r:id="rId94" xr:uid="{4497CAC4-1492-491E-9892-1BD4ED779D36}"/>
+    <hyperlink ref="B9" r:id="rId1" xr:uid="{30D31D35-DAEB-41FE-8584-24E31F75519E}"/>
+    <hyperlink ref="B10" r:id="rId2" xr:uid="{5198BC62-CBD5-4CD4-B28B-23E4DE3A47FF}"/>
+    <hyperlink ref="B11" r:id="rId3" xr:uid="{91DE0745-0C6C-4B23-810E-23F93787A5F2}"/>
+    <hyperlink ref="B12" r:id="rId4" xr:uid="{CBA5CC3E-3121-4A86-919C-EB8E0529C071}"/>
+    <hyperlink ref="B13" r:id="rId5" xr:uid="{E3BB5D46-D4E9-4D40-A770-53C77705B309}"/>
+    <hyperlink ref="B14" r:id="rId6" xr:uid="{187B4948-CF43-4452-922B-DD40F6C17C4E}"/>
+    <hyperlink ref="A15" r:id="rId7" display="https://www.agenziaentrate.gov.it/portale/enti-gestori-delle-aree-protette-2024" xr:uid="{04293583-0231-42B0-9B6D-67248923F9C5}"/>
+    <hyperlink ref="B15" r:id="rId8" xr:uid="{167AA414-07C8-41DF-BF22-3DAC32864916}"/>
+    <hyperlink ref="A16" r:id="rId9" display="https://www.agenziaentrate.gov.it/portale/enti-del-terzo-settore-e-onlus-2023" xr:uid="{085E4620-B75D-484A-99D5-04916EDF073A}"/>
+    <hyperlink ref="B16" r:id="rId10" xr:uid="{A57C72D1-090D-406B-B8EA-86833706DB2E}"/>
+    <hyperlink ref="A17" r:id="rId11" display="https://www.agenziaentrate.gov.it/portale/ricerca-scientifica-2023" xr:uid="{0BF1B728-0DCE-4F1D-AFC7-184DC487015B}"/>
+    <hyperlink ref="B17" r:id="rId12" xr:uid="{2313E86F-EBDA-44D0-A425-FA79E0F21639}"/>
+    <hyperlink ref="A18" r:id="rId13" display="https://www.agenziaentrate.gov.it/portale/ricerca-sanitaria-2023" xr:uid="{FCEFB34E-674A-43E6-8F67-D359B003339A}"/>
+    <hyperlink ref="B18" r:id="rId14" xr:uid="{5DEE8BA2-05B4-46E5-B403-548902D74E52}"/>
+    <hyperlink ref="A19" r:id="rId15" display="https://www.agenziaentrate.gov.it/portale/attivita-svolte-dai-comuni-2023" xr:uid="{8AC218D4-94E2-4F1A-A383-31576D3DEB3F}"/>
+    <hyperlink ref="B19" r:id="rId16" xr:uid="{1930118C-E720-4212-82EF-49AE2802BE33}"/>
+    <hyperlink ref="A20" r:id="rId17" display="https://www.agenziaentrate.gov.it/portale/associazioni-sportive-dilettantistiche-2023" xr:uid="{15B89EFB-1F1F-4A61-A563-3A8337E23B04}"/>
+    <hyperlink ref="B20" r:id="rId18" xr:uid="{7E186F42-B301-4580-86D3-ADEAE1B10C86}"/>
+    <hyperlink ref="A21" r:id="rId19" display="https://www.agenziaentrate.gov.it/portale/enti-dei-beni-culturali-e-paesaggistici-2023" xr:uid="{A7A4309E-F81D-4C64-AA74-E7E3EBD52B0B}"/>
+    <hyperlink ref="B21" r:id="rId20" xr:uid="{C6E01281-1AE6-4901-8DAF-DF706FAA7B87}"/>
+    <hyperlink ref="A22" r:id="rId21" display="https://www.agenziaentrate.gov.it/portale/Enti-gestori-delle-aree-protette-2023" xr:uid="{25407C4D-FCCC-4241-BFDD-2ED1508E679F}"/>
+    <hyperlink ref="B22" r:id="rId22" xr:uid="{D2A3AD40-F054-4CB9-B23D-E0E7CB1FF5F5}"/>
+    <hyperlink ref="A23" r:id="rId23" display="https://www.agenziaentrate.gov.it/portale/enti-del-terzo-settore-e-onlus-23" xr:uid="{9AEE31A2-AF07-48B6-BD31-43782B2AE493}"/>
+    <hyperlink ref="B23" r:id="rId24" xr:uid="{DC38C048-5DEA-4205-8682-8747199D0A66}"/>
+    <hyperlink ref="A24" r:id="rId25" display="https://www.agenziaentrate.gov.it/portale/ricerca-scientifica-23" xr:uid="{4D97CD3A-691C-4E94-9119-A8CE36AEF0F9}"/>
+    <hyperlink ref="B24" r:id="rId26" xr:uid="{44F182CE-2362-40AB-9947-B665627BA327}"/>
+    <hyperlink ref="A25" r:id="rId27" display="https://www.agenziaentrate.gov.it/portale/ricerca-sanitaria" xr:uid="{6B2ACB9C-5F1E-4B8D-AAD9-40779502F7C0}"/>
+    <hyperlink ref="B25" r:id="rId28" xr:uid="{6167BE59-0896-4BF1-95A7-ABC7932C8832}"/>
+    <hyperlink ref="A26" r:id="rId29" display="https://www.agenziaentrate.gov.it/portale/attivita-svolte-dai-comuni-23" xr:uid="{A5FFFACC-7FC2-4095-A036-E4F0996D6773}"/>
+    <hyperlink ref="B26" r:id="rId30" xr:uid="{9AFAC604-E64A-4F31-871C-7B382794034C}"/>
+    <hyperlink ref="A27" r:id="rId31" display="https://www.agenziaentrate.gov.it/portale/associazioni-sportive-dilettantistiche-asd-23" xr:uid="{494E0552-E012-419B-B906-B0A213732E2B}"/>
+    <hyperlink ref="B27" r:id="rId32" xr:uid="{8A572FAA-1F83-4626-9267-199301E2975B}"/>
+    <hyperlink ref="A28" r:id="rId33" display="https://www.agenziaentrate.gov.it/portale/beni-culturali-e-paesaggistici-23" xr:uid="{6A643E59-4432-4D8D-A950-ED24B3B8E28D}"/>
+    <hyperlink ref="B28" r:id="rId34" xr:uid="{6DA59AD1-E4A2-4816-9728-657C4FC30FCE}"/>
+    <hyperlink ref="A29" r:id="rId35" display="https://www.agenziaentrate.gov.it/portale/documents/20143/4443043/5XM-AF2022+-+AREE+PROTETTE+-+AMMESSI.pdf/51ed59be-2418-4db3-39c5-61ab02064f31?t=1687459725347" xr:uid="{CC4EEEDC-80FE-43B8-B4CF-9D66911363A1}"/>
+    <hyperlink ref="B29" r:id="rId36" xr:uid="{2566C3DA-FFFE-4252-94BF-8881E575DFFC}"/>
+    <hyperlink ref="A30" r:id="rId37" display="https://www.agenziaentrate.gov.it/portale/enti-volontariato-ammessi-esclusi-af-2021" xr:uid="{9BA21E0C-3739-40DF-928D-9E486BE298D7}"/>
+    <hyperlink ref="B30" r:id="rId38" xr:uid="{1D149A7A-71C3-45F4-8183-05B3772DF65C}"/>
+    <hyperlink ref="A31" r:id="rId39" display="https://www.agenziaentrate.gov.it/portale/ricerca-scientifica-ammessi-esclusi-af-2021" xr:uid="{16CA7436-978D-436A-A145-2219F6A5B89D}"/>
+    <hyperlink ref="B31" r:id="rId40" xr:uid="{F1C12662-2C07-4026-B6E3-BDC34A17ED64}"/>
+    <hyperlink ref="A32" r:id="rId41" display="https://www.agenziaentrate.gov.it/portale/ricerca-sanitaria-ammessi-esclusi-af-2021" xr:uid="{E9C79AAF-AB8D-457A-94E6-1290C2AD8224}"/>
+    <hyperlink ref="B32" r:id="rId42" xr:uid="{A76D6B3E-9171-4A69-A861-1FE384E8780B}"/>
+    <hyperlink ref="A33" r:id="rId43" display="https://www.agenziaentrate.gov.it/portale/attivit%C3%A0-svolte-dai-comuni-ammessi-esclusi-af-2021" xr:uid="{E71B9303-433E-424D-9777-DED52F66AA86}"/>
+    <hyperlink ref="B33" r:id="rId44" xr:uid="{E462E970-138F-4E58-A964-4B006459EF58}"/>
+    <hyperlink ref="A34" r:id="rId45" display="https://www.agenziaentrate.gov.it/portale/asd-ammessi-esclusi-af-2021" xr:uid="{764031F2-DE1C-49D3-BC48-4A1E1B88CFC1}"/>
+    <hyperlink ref="B34" r:id="rId46" xr:uid="{539B33DD-6A26-48A1-9E08-C88C2DE0118B}"/>
+    <hyperlink ref="A35" r:id="rId47" display="https://www.agenziaentrate.gov.it/portale/enti-dei-beni-culturali-e-paesaggistici-af-2021" xr:uid="{6E07C45A-0CC9-451B-9A44-62CF48B5DDB2}"/>
+    <hyperlink ref="B35" r:id="rId48" xr:uid="{D15CB439-E862-438C-83AA-44446BB01F0D}"/>
+    <hyperlink ref="A36" r:id="rId49" display="https://www.agenziaentrate.gov.it/portale/enti-gestori-aree-protette-ammessi-esclusi-af-2021" xr:uid="{C148DC0D-AC6F-4A42-B621-B73C1F43EFC1}"/>
+    <hyperlink ref="B36" r:id="rId50" xr:uid="{F09EC905-FEED-44F2-9897-181EEF93E417}"/>
+    <hyperlink ref="A37" r:id="rId51" display="https://www.agenziaentrate.gov.it/portale/ammessi-ed-esclusi-enti-del-volontariato-5x1000-2020" xr:uid="{47EB5E9E-58EA-4AEB-ADF6-35FA9C29CCC1}"/>
+    <hyperlink ref="B37" r:id="rId52" xr:uid="{65EE7DC2-3FEE-4E1A-B0C9-EF80822986AD}"/>
+    <hyperlink ref="A38" r:id="rId53" display="https://www.agenziaentrate.gov.it/portale/ricerca-scientifica-ammessi-ed-esclusi-5x1000-2020" xr:uid="{2ABBBE77-E908-44AF-A47A-298685FDB9A1}"/>
+    <hyperlink ref="B38" r:id="rId54" xr:uid="{92578B0D-0F12-49D1-9027-D9E69DAC86BF}"/>
+    <hyperlink ref="A39" r:id="rId55" display="https://www.agenziaentrate.gov.it/portale/ricerca-sanitaria-ammessi-esclusi-5x1000-2020" xr:uid="{1DF48004-D32B-4E4C-9702-E9C312287385}"/>
+    <hyperlink ref="B39" r:id="rId56" xr:uid="{37F5CDDA-36F0-437F-B9CC-D62C6616BA05}"/>
+    <hyperlink ref="A40" r:id="rId57" display="https://www.agenziaentrate.gov.it/portale/attivita-svolte-dai-comuni-ammessi-esclusi-5x1000-2020" xr:uid="{D8DD0AE9-1899-4BA6-8B0A-0F2D093B76DB}"/>
+    <hyperlink ref="B40" r:id="rId58" xr:uid="{99E94FAF-1EAA-42E2-B796-64CA7766A469}"/>
+    <hyperlink ref="A41" r:id="rId59" display="https://www.agenziaentrate.gov.it/portale/associazioni-sportive-dilettantistiche-ammessi-esclusi-5x1000-2020" xr:uid="{9301FF8E-783C-4D1D-A563-9B8D9103AAD2}"/>
+    <hyperlink ref="B41" r:id="rId60" xr:uid="{48DCD4A3-6030-497A-B517-4D00A042DBDA}"/>
+    <hyperlink ref="A42" r:id="rId61" display="https://www.agenziaentrate.gov.it/portale/enti-dei-beni-culturali-e-paesaggistici-ammessi-esclusi-5x1000-2020" xr:uid="{4895397C-8ABA-40E7-BD63-606256D85F4E}"/>
+    <hyperlink ref="B42" r:id="rId62" xr:uid="{5F032F00-8FA5-4008-9D68-61676A3EB666}"/>
+    <hyperlink ref="A43" r:id="rId63" display="https://www.agenziaentrate.gov.it/portale/enti-gestori-delle-aree-protette-esclusi-ammessi-5x1000-2020" xr:uid="{629A3CF7-2344-43A6-A2A9-FA8AA437DB5B}"/>
+    <hyperlink ref="B43" r:id="rId64" xr:uid="{CF95AB0E-0728-4EF7-A640-409F1CD4AB71}"/>
+    <hyperlink ref="A44" r:id="rId65" display="https://www.agenziaentrate.gov.it/portale/enti-del-volontariato-2019" xr:uid="{BBC1505A-8B11-42FD-9B9F-41209ACBA0FD}"/>
+    <hyperlink ref="B44" r:id="rId66" xr:uid="{C22762C1-D955-4AC5-94F5-1638121AC290}"/>
+    <hyperlink ref="A45" r:id="rId67" display="https://www.agenziaentrate.gov.it/portale/ricerca-scientifica1" xr:uid="{2C4CD3DE-CA60-415A-A009-7FFB1FD5D20F}"/>
+    <hyperlink ref="B45" r:id="rId68" xr:uid="{2C4AD919-3338-4279-AB57-269DBE61C6DF}"/>
+    <hyperlink ref="A46" r:id="rId69" display="https://www.agenziaentrate.gov.it/portale/ricerca-sanitaria-2019" xr:uid="{A48DD348-E1DA-41F4-BF94-AFD03AB52587}"/>
+    <hyperlink ref="B46" r:id="rId70" xr:uid="{08761D35-6CEF-4E66-AECF-7BDA34E3A352}"/>
+    <hyperlink ref="A47" r:id="rId71" display="https://www.agenziaentrate.gov.it/portale/attivit%C3%A0-svolte-dai-comuni-2019" xr:uid="{7F8062F9-1F41-498B-A000-15E8D2F515DB}"/>
+    <hyperlink ref="B47" r:id="rId72" xr:uid="{7B2C9579-C1F2-4F40-8472-1FB31040D65E}"/>
+    <hyperlink ref="A48" r:id="rId73" display="https://www.agenziaentrate.gov.it/portale/associazioni-sportive-dilettantistiche-2019" xr:uid="{616F6478-5442-4D2A-9453-58F1DE0936D1}"/>
+    <hyperlink ref="B48" r:id="rId74" xr:uid="{D31D3A05-1DD1-432D-83D1-DC41E796E6D0}"/>
+    <hyperlink ref="A49" r:id="rId75" display="https://www.agenziaentrate.gov.it/portale/enti-dei-beni-culturali-e-paesaggistici-2019" xr:uid="{354CF7D3-3609-4D21-B12B-983CA359AB53}"/>
+    <hyperlink ref="B49" r:id="rId76" xr:uid="{BF09495E-2AD3-4A0E-ADE1-BAEE07B3C691}"/>
+    <hyperlink ref="A50" r:id="rId77" display="https://www.agenziaentrate.gov.it/portale/enti-gestori-delle-aree-protette-2019" xr:uid="{E85BC395-BE9A-4A48-9D6D-518BA12858E5}"/>
+    <hyperlink ref="B50" r:id="rId78" xr:uid="{6D46722B-E5A6-4B53-B2CE-6CDEBEABFE55}"/>
+    <hyperlink ref="A14" r:id="rId79" display="https://www.agenziaentrate.gov.it/portale/enti-dei-beni-culturali-e-paesaggistici-2024" xr:uid="{67F61C3C-BA70-449F-AA2F-0594A7373756}"/>
+    <hyperlink ref="A13" r:id="rId80" display="https://www.agenziaentrate.gov.it/portale/associazioni-sportive-dilettantistiche-2024" xr:uid="{7901A471-EF6F-4134-9979-1C8AB5CD7DB8}"/>
+    <hyperlink ref="A12" r:id="rId81" display="https://www.agenziaentrate.gov.it/portale/attivit%C3%A0-svolte-dai-comuni-2024" xr:uid="{A8ED647E-0122-4E28-9F3B-D5C740C35384}"/>
+    <hyperlink ref="A11" r:id="rId82" display="https://www.agenziaentrate.gov.it/portale/ricerca-sanitaria-2024" xr:uid="{B2B0FDC3-8D60-426C-B6A2-EE7E293064CC}"/>
+    <hyperlink ref="A10" r:id="rId83" display="https://www.agenziaentrate.gov.it/portale/ricerca-scientifica-2024" xr:uid="{F1F7AF15-DA2C-4E02-BC15-B87572759553}"/>
+    <hyperlink ref="A9" r:id="rId84" display="https://www.agenziaentrate.gov.it/portale/enti-del-terzo-settore-e-onlus-2024" xr:uid="{0746E94C-A9B6-4BDA-9560-426C170FE9FD}"/>
+    <hyperlink ref="A2" r:id="rId85" display="https://www.agenziaentrate.gov.it/portale/enti-del-terzo-settore" xr:uid="{91A7EC19-28DD-4499-B2B0-FBD6125B9962}"/>
+    <hyperlink ref="A3" r:id="rId86" display="https://www.agenziaentrate.gov.it/portale/ricerca-scientifica2" xr:uid="{3655F944-3E8F-45F0-B339-AEDA9A660C9B}"/>
+    <hyperlink ref="A4" r:id="rId87" display="https://www.agenziaentrate.gov.it/portale/ricerca-sanitaria1" xr:uid="{F54210A0-3299-49A6-9D92-EE2A0FF4B166}"/>
+    <hyperlink ref="A5" r:id="rId88" display="https://www.agenziaentrate.gov.it/portale/attivit%C3%A0-svolte-dai-comuni" xr:uid="{BD9CC269-D6A5-4FCB-B017-DD30CB134963}"/>
+    <hyperlink ref="A6" r:id="rId89" display="https://www.agenziaentrate.gov.it/portale/associazioni-sportive-dilettantistiche1" xr:uid="{2B9BBA5C-2532-459F-90A6-EBE166607619}"/>
+    <hyperlink ref="A7" r:id="rId90" display="https://www.agenziaentrate.gov.it/portale/enti-dei-beni-culturali-e-paesaggistici" xr:uid="{B1718181-8A1A-490D-85DA-A3D6B3EF04F9}"/>
+    <hyperlink ref="A8" r:id="rId91" display="https://www.agenziaentrate.gov.it/portale/enti-gestori-delle-aree-protette" xr:uid="{1457A610-D7EF-47F7-B230-06A652E068A9}"/>
+    <hyperlink ref="B2" r:id="rId92" location=":~:text=in%20formato%20pdf-,Enti%20del%20Terzo%20Settore,-Ricerca%20scientifica" xr:uid="{B33D9761-5140-4215-9B7B-B694D4A853D8}"/>
+    <hyperlink ref="B3" r:id="rId93" xr:uid="{531DF830-A2E8-41DC-B47E-712DE762215C}"/>
+    <hyperlink ref="B4" r:id="rId94" location=":~:text=Ricerca%20scientifica-,Ricerca%20sanitaria,-Attivit%C3%A0%20svolte%20dai" xr:uid="{9A447999-EAC9-4642-A396-4B8BFAAAECEA}"/>
+    <hyperlink ref="B5" r:id="rId95" location=":~:text=Attivit%C3%A0%20svolte%20dai%20comuni" xr:uid="{0AEE14E0-8B3B-4BBD-BACC-DFA9F3E72388}"/>
+    <hyperlink ref="B6" r:id="rId96" location=":~:text=svolte%20dai%20comuni-,Associazioni%20sportive%20dilettantistiche,-Enti%20dei%20beni" xr:uid="{9D631D43-B6F6-4E53-B2F6-988E76ED2FBD}"/>
+    <hyperlink ref="B7" r:id="rId97" location=":~:text=Associazioni%20sportive%20dilettantistiche-,Enti%20dei%20beni%20culturali%20e%20paesaggistici,-Enti%20gestori%20delle" xr:uid="{42D07CB3-8857-44F2-ACFB-4763757ADD76}"/>
+    <hyperlink ref="B8" r:id="rId98" location=":~:text=culturali%20e%20paesaggistici-,Enti%20gestori%20delle%20aree%20protette,-L%27Agenzia" xr:uid="{E2C3F87D-D059-4AFF-929F-25DDA2852F96}"/>
   </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId99"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E45AC1D-C4C3-4C5D-AEC6-B166B0B5C420}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/categorie.xlsx
+++ b/categorie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/61197a8ee6b2bca5/Documenti/Siti Internert/5x1000_prod/5x1000.almagioni.com/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="11_38BE3B91B9C9449F3341FF0824850D43D1462CD6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8AF3F87-6569-4806-9C4A-326705CB901A}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="11_38BE3B91B9C9449F3341FF0824850D43D1462CD6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF9026EB-8894-41BB-B8B2-375C6F1BFED2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -197,25 +197,25 @@
     <t>Enti del Terzo Settore</t>
   </si>
   <si>
-    <t>https://www.agenziaentrate.gov.it/portale/elenchi-ammessi-ed-esclusi2#:~:text=in%20formato%20pdf-,Enti%20del%20Terzo%20Settore,-Ricerca%20scientifica</t>
-  </si>
-  <si>
     <t>https://www.agenziaentrate.gov.it/portale/ricerca-scientifica2</t>
   </si>
   <si>
-    <t>https://www.agenziaentrate.gov.it/portale/elenchi-ammessi-ed-esclusi2#:~:text=Ricerca%20scientifica-,Ricerca%20sanitaria,-Attivit%C3%A0%20svolte%20dai</t>
-  </si>
-  <si>
-    <t>https://www.agenziaentrate.gov.it/portale/elenchi-ammessi-ed-esclusi2#:~:text=Attivit%C3%A0%20svolte%20dai%20comuni</t>
-  </si>
-  <si>
-    <t>https://www.agenziaentrate.gov.it/portale/elenchi-ammessi-ed-esclusi2#:~:text=svolte%20dai%20comuni-,Associazioni%20sportive%20dilettantistiche,-Enti%20dei%20beni</t>
-  </si>
-  <si>
-    <t>https://www.agenziaentrate.gov.it/portale/elenchi-ammessi-ed-esclusi2#:~:text=Associazioni%20sportive%20dilettantistiche-,Enti%20dei%20beni%20culturali%20e%20paesaggistici,-Enti%20gestori%20delle</t>
-  </si>
-  <si>
-    <t>https://www.agenziaentrate.gov.it/portale/elenchi-ammessi-ed-esclusi2#:~:text=culturali%20e%20paesaggistici-,Enti%20gestori%20delle%20aree%20protette,-L%27Agenzia</t>
+    <t>https://www.agenziaentrate.gov.it/portale/enti-del-terzo-settore</t>
+  </si>
+  <si>
+    <t>https://www.agenziaentrate.gov.it/portale/ricerca-sanitaria1</t>
+  </si>
+  <si>
+    <t>https://www.agenziaentrate.gov.it/portale/attivit%C3%A0-svolte-dai-comuni</t>
+  </si>
+  <si>
+    <t>https://www.agenziaentrate.gov.it/portale/associazioni-sportive-dilettantistiche1</t>
+  </si>
+  <si>
+    <t>https://www.agenziaentrate.gov.it/portale/enti-dei-beni-culturali-e-paesaggistici</t>
+  </si>
+  <si>
+    <t>https://www.agenziaentrate.gov.it/portale/enti-gestori-delle-aree-protette</t>
   </si>
 </sst>
 </file>
@@ -234,6 +234,7 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -545,7 +546,7 @@
         <v>56</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C2" s="2">
         <v>2025</v>
@@ -556,7 +557,7 @@
         <v>18</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C3" s="2">
         <v>2025</v>
@@ -1173,16 +1174,10 @@
     <hyperlink ref="A6" r:id="rId89" display="https://www.agenziaentrate.gov.it/portale/associazioni-sportive-dilettantistiche1" xr:uid="{2B9BBA5C-2532-459F-90A6-EBE166607619}"/>
     <hyperlink ref="A7" r:id="rId90" display="https://www.agenziaentrate.gov.it/portale/enti-dei-beni-culturali-e-paesaggistici" xr:uid="{B1718181-8A1A-490D-85DA-A3D6B3EF04F9}"/>
     <hyperlink ref="A8" r:id="rId91" display="https://www.agenziaentrate.gov.it/portale/enti-gestori-delle-aree-protette" xr:uid="{1457A610-D7EF-47F7-B230-06A652E068A9}"/>
-    <hyperlink ref="B2" r:id="rId92" location=":~:text=in%20formato%20pdf-,Enti%20del%20Terzo%20Settore,-Ricerca%20scientifica" xr:uid="{B33D9761-5140-4215-9B7B-B694D4A853D8}"/>
-    <hyperlink ref="B3" r:id="rId93" xr:uid="{531DF830-A2E8-41DC-B47E-712DE762215C}"/>
-    <hyperlink ref="B4" r:id="rId94" location=":~:text=Ricerca%20scientifica-,Ricerca%20sanitaria,-Attivit%C3%A0%20svolte%20dai" xr:uid="{9A447999-EAC9-4642-A396-4B8BFAAAECEA}"/>
-    <hyperlink ref="B5" r:id="rId95" location=":~:text=Attivit%C3%A0%20svolte%20dai%20comuni" xr:uid="{0AEE14E0-8B3B-4BBD-BACC-DFA9F3E72388}"/>
-    <hyperlink ref="B6" r:id="rId96" location=":~:text=svolte%20dai%20comuni-,Associazioni%20sportive%20dilettantistiche,-Enti%20dei%20beni" xr:uid="{9D631D43-B6F6-4E53-B2F6-988E76ED2FBD}"/>
-    <hyperlink ref="B7" r:id="rId97" location=":~:text=Associazioni%20sportive%20dilettantistiche-,Enti%20dei%20beni%20culturali%20e%20paesaggistici,-Enti%20gestori%20delle" xr:uid="{42D07CB3-8857-44F2-ACFB-4763757ADD76}"/>
-    <hyperlink ref="B8" r:id="rId98" location=":~:text=culturali%20e%20paesaggistici-,Enti%20gestori%20delle%20aree%20protette,-L%27Agenzia" xr:uid="{E2C3F87D-D059-4AFF-929F-25DDA2852F96}"/>
+    <hyperlink ref="B3" r:id="rId92" xr:uid="{531DF830-A2E8-41DC-B47E-712DE762215C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId99"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId93"/>
 </worksheet>
 </file>
 
